--- a/docs/design/怪物数据表.xlsx
+++ b/docs/design/怪物数据表.xlsx
@@ -30,10 +30,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -42,16 +41,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004F3B78"/>
+        <fgColor rgb="004A4E69"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -59,30 +53,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C9C9C9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00C9C9C9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C9C9C9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C9C9C9"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -157,6 +139,541 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -448,670 +965,818 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>图标</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>移速</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>技能1</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>技能2</t>
+          <t>行为(behavior)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>技能3</t>
+          <t>独特技能</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>独特技能</t>
+          <t>技能CD(s)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>弹速</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>掉金</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>经验</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>出现关卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>slime</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>史莱姆</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>弹跳(leap)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>分裂增殖(split)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>分裂增殖[split]</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" s="2" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>level_1,level_2,level_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>bat</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>蝙蝠</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>超声尖啸(projectile_spread)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>超声尖啸[projectile_spread]</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>scream</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>scream</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="K3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" s="2" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>level_1,level_2,level_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>ghost</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>幽灵</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" s="2" t="n">
         <v>78</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>相位穿行(charge)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>相位穿行[charge]</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" s="2" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>level_2,level_3,level_4,level_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>goblin</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>哥布林</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>投石(lava_eruption)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>投石[lava_eruption]</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" s="2" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>level_1,level_2,level_3,level_4,level_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>goblin_archer</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>哥布林弓手</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>多重箭(projectile_spread)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>多重箭[projectile_spread]</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="K6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" s="2" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>level_2,level_3,level_4,level_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>skeleton</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>骷髅</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>盾反(self_buff)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>盾反[self_buff]</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" s="2" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>level_3,level_4,level_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>imp</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>小恶魔</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>火焰闪现(blink)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>火焰闪现[blink]</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>triple</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>triple</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="K8" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" s="2" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>level_4,level_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>wizard</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>秘法巫师</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>奥术弹环(ring_barrage)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>奥术弹环[ring_barrage]</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" s="2" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>level_1,level_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>bomber</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>爆裂者</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>主动自爆(self_destruct)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>主动自爆[self_destruct]</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>bomb</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>bomb</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" s="2" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>level_4,level_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>charger</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>冲锋兽</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>践踏震击(root_zone)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>践踏震击[root_zone]</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>stomp</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>stomp</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" s="2" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>level_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>healer</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>幽暗巫医</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>死亡诅咒(homing_shot)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>死亡诅咒[homing_shot]</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>curse</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>curse</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" s="2" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>level_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>crystal_sentry</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>水晶哨兵</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>棱镜激光(beam)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>棱镜激光[beam]</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>sniper</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>sniper</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="K13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" s="2" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>level_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>spider</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>毒蛛</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>毒网(zone_slow)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>毒网[zone_slow]</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" s="2" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>level_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>mimic_block</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>魔像方块</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>陷阱爆发(lava_eruption)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>陷阱爆发[lava_eruption]</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="K15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" s="2" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>level_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>specter</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>幽魂法师</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>暗影偷袭(stealth_ambush)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>暗影偷袭[stealth_ambush]</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>vanish</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>vanish</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="K16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" s="2" t="n">
         <v>14</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>level_2</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1121,1820 +1786,2196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>图标</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>BossID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>移速</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>技能ID</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>技能名</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>关键参数</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>冷却(s)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>阶段门控</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>预告</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>独特机制</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>slime_king</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>史莱姆王</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>split_shot</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>散射</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>projectile_spread</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>shots=5 speed=190</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>shots=5; bullet_speed=190; windup=0.6</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>slime_king</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>史莱姆王</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>slime_ring</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>弹幕环</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>ring_barrage</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>shots=18 waves=2 speed=170</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>shots=18; waves=2; bullet_speed=170; windup=0.8</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
         <v>6.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>slime_king</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>史莱姆王</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>leap</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>跳跃</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>leap</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>radius=120 dmg=1.5x</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>radius=120; damage_mult=1.5; windup=0.9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>slime_king</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>史莱姆王</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>split_frenzy</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>分裂召唤</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>summon_minions</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>count=3</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>count=3; windup=0.7</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>slime_king</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>史莱姆王</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>split_self</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>自我分裂</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>split</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>count=2</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>count=2; windup=0.6</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" s="2" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>tree_golem</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>树精守卫</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>root_vine</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>根须缠绕</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>root_zone</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>radius=90 dur=2.0 dps=3.5%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>radius=90; duration=2.0; dps_mult=0.035; windup=0.8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
         <v>7.5</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>tree_golem</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>树精守卫</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>seed_barrage</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>种子散射</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>projectile_spread</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>shots=10 speed=160</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>shots=10; bullet_speed=160; windup=0.7</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
         <v>5.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>tree_golem</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>树精守卫</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>seed_ring</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>种子弹环</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>ring_barrage</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>shots=16 waves=1 speed=150</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>shots=16; waves=1; bullet_speed=150; windup=0.9</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>tree_golem</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>树精守卫</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>bark_armor</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>树皮护甲</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>self_buff</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>armor=0.5 dur=4.0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>armor=0.5; duration=4.0; windup=0.5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>tree_golem</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>树精守卫</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>vine_thralls</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>藤蔓召唤</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>summon_wave</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>count=3+1精英</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>count=3; elite_count=1; windup=0.8</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>tree_golem</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>树精守卫</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>root_spikes</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>根须地刺</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>spike_trail</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>count=6 spacing=64 radius=34</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>count=6; spacing=64; radius=34; delay=0.6; interval=0.12; damage_mult=0.9; windup=0.8</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" s="2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>skeleton_king</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>骷髅王</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>bone_volley</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>骨矢齐射</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>projectile_spread</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>shots=7 spread=30 speed=200</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>shots=7; spread=30; bullet_speed=200; windup=0.6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>skeleton_king</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>骷髅王</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>raise_dead</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>亡者复苏</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>summon_minions</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>count=4</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>count=4; windup=0.8</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>skeleton_king</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>骷髅王</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>bone_ring</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>骨环弹幕</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>ring_barrage</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>shots=16 waves=2 speed=200</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>shots=16; waves=2; bullet_speed=200; windup=0.7</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>skeleton_king</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>骷髅王</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>death_zone</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>死亡领域</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>root_zone</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>radius=120 dur=3.0 dps=10%</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>radius=120; duration=3.0; dps_mult=0.1; windup=0.9</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>skeleton_king</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>骷髅王</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>bone_sweep</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>骨刃扫射</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>sweep</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>angle=120 dur=1.6</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>duration=1.6; sweep_angle=120; windup=1.0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" s="2" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>imp_king</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>熔岩魔王</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>fire_triple</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>烈焰三连</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>projectile_spread</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>shots=5 spread=24 speed=220</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>shots=5; spread=24; bullet_speed=220; windup=0.5</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>imp_king</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>熔岩魔王</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>flame_ring</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>烈焰弹环</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>ring_barrage</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>shots=20 waves=2 speed=200</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>shots=20; waves=2; bullet_speed=200; windup=0.7</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
         <v>5.5</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>imp_king</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>熔岩魔王</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>lava_eruption</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>熔岩喷发</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>lava_eruption</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>count=5 radius=58</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>count=5; radius=58; windup=0.9</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
         <v>6.5</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>imp_king</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>熔岩魔王</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>lava_charge</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>熔岩冲锋</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>charge</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>speed=4x trail=fire</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>speed_mult=4.0; trail=fire; windup=0.8</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>imp_king</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>熔岩魔王</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>fire_imps</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>火魔召唤</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>summon_wave</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>count=3+1精英</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>count=3; elite_count=1; windup=0.8</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>imp_king</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>熔岩魔王</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>flame_spiral</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>烈焰螺旋</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>spiral</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>shots=10 speed=160 dur=1.4</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>shots=10; bullet_speed=160; duration=1.4; ring_interval=0.14; offset=18; windup=0.9</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>imp_king</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>熔岩魔王</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>fire_wall</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>火墙</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>wall</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>count=8 radius=46</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>count=8; radius=46; delay=0.4; interval=0.12; damage_mult=1.0; windup=0.9</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" s="2" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>ancient_guardian</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>远古守卫</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>light_beam</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>圣光射线</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>beam</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>dur=1.5</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>duration=1.5; windup=1.0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n">
         <v>6.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>ancient_guardian</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>远古守卫</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>holy_ring</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>圣环弹幕</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>ring_barrage</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>shots=24 waves=2 speed=180</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>shots=24; waves=2; bullet_speed=180; windup=1.0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>ancient_guardian</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>远古守卫</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>shield_ring</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>护盾环</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>shield_ring</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>dur=5.0</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>duration=5.0; windup=0.6</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>ancient_guardian</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>远古守卫</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>summon_elite</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>精英召唤</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>summon_minions</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>count=4 elite</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>count=4; elite=True; windup=0.8</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>ancient_guardian</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>远古守卫</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>seeker_light</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>圣光追踪</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>homing_shot</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>count=4 speed=135 turn=3.0</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>count=4; bullet_speed=135; turn_rate=3.0; lifetime=4.0; windup=0.8</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>ancient_guardian</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>远古守卫</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>guardian_blink</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>守卫闪现</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>blink</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>radius=110 dmg=1.6x</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>radius=110; damage_mult=1.6; windup=0.9</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" s="2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>final_god</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>古神</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D31" t="n">
-        <v>34</v>
-      </c>
-      <c r="E31" t="n">
-        <v>60</v>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="D31" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>void_barrage</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>虚空齐射</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>projectile_spread</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>shots=14 speed=180</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>shots=14; bullet_speed=180; windup=0.6</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>final_god</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>古神</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D32" t="n">
-        <v>34</v>
-      </c>
-      <c r="E32" t="n">
-        <v>60</v>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="D32" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>void_ring</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>虚空弹环</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>ring_barrage</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>shots=24 waves=2 speed=210</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>shots=24; waves=2; bullet_speed=210; windup=1.0</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>final_god</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>古神</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D33" t="n">
-        <v>34</v>
-      </c>
-      <c r="E33" t="n">
-        <v>60</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="D33" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>whirl_laser</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>旋转激光</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>whirl_laser</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>dur=2.5</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>duration=2.5; windup=1.0</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>final_god</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>古神</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D34" t="n">
-        <v>34</v>
-      </c>
-      <c r="E34" t="n">
-        <v>60</v>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="D34" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>void_minions</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>虚空召唤</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>summon_wave</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>count=4+1精英</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>count=4; elite_count=1; windup=0.9</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>final_god</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>古神</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D35" t="n">
-        <v>34</v>
-      </c>
-      <c r="E35" t="n">
-        <v>60</v>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="D35" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>meteor_storm</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>陨石风暴</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>meteor</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>count=10 radius=70</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>count=10; radius=70; windup=1.2</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n">
         <v>8.5</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>final_god</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>古神</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D36" t="n">
-        <v>34</v>
-      </c>
-      <c r="E36" t="n">
-        <v>60</v>
-      </c>
-      <c r="F36" t="inlineStr">
+      <c r="D36" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>void_spiral</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>虚空螺旋</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>spiral</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>shots=12 speed=170 dur=1.8</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>shots=12; bullet_speed=170; duration=1.8; ring_interval=0.12; offset=15; windup=1.0</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>final_god</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>古神</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D37" t="n">
-        <v>34</v>
-      </c>
-      <c r="E37" t="n">
-        <v>60</v>
-      </c>
-      <c r="F37" t="inlineStr">
+      <c r="D37" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>void_seeker</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>虚空追踪</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>homing_shot</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>count=3 speed=140</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>count=3; bullet_speed=140; turn_rate=3.0; lifetime=4.0; windup=0.9</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>final_god</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>古神</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D38" t="n">
-        <v>34</v>
-      </c>
-      <c r="E38" t="n">
-        <v>60</v>
-      </c>
-      <c r="F38" t="inlineStr">
+      <c r="D38" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>ancient_enrage</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>远古狂暴</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>enrage</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>speed=1.3x cd=0.7x</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>speed_mult=1.3; cd_mult=0.7; windup=0.1</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" s="2" t="n">
         <v>3</v>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2944,430 +3985,446 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>技能ID</t>
+          <t>行为ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>类型</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>类型</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>参数建议</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>预告方式</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>适用怪类型</t>
+          <t>适用怪</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>line_shot</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>直线弹幕</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>projectile_spread</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>shots 1-2 / spread 0-10° / bullet_speed 180-220 / windup 0.3-0.5 / damage_mult 1.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>所有远程小怪（哨兵/弓手/小恶魔）</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>分裂增殖</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>半血时主动分裂 2 只弱化小怪</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>slime</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>fan_shot</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>扇形弹幕</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>projectile_spread</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>shots 3-5 / spread 30-45° / bullet_speed 160-190 / windup 0.4-0.6</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>近战接近时的反击技，打断玩家贴脸输出</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>scream</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>超声尖啸</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>5 发扇形音波打散玩家</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>bat</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>snipe_shot</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>蓄力狙击</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>projectile_spread</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>shots 1 / damage_mult 2.0-2.5 / pierce true / bullet_speed 300-360 / windup 0.8-1.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>远程压制位（弓手/幽魂法师），压血线用</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>相位穿行</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>周期无敌 3 倍速穿越</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ghost</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>homing_bolt</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>投石</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>远程落点圈逼迫走位</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>goblin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>多重箭</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5 箭扇形清走位</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>goblin_archer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>盾反</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1.2s 高甲 70% 减伤</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>skeleton</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>triple</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>三连射</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3 发扇形弹幕</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>imp / 精英</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>巫师施法</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>前摇后大号火球</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>bomb</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>自爆</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>蓄力/死亡自爆</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>bomber</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>stomp</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>践踏震击</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>脚下减速圈封侧闪</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>charger</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>curse</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>死亡诅咒</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>追踪弹</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>homing_shot</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>count 1-2 / turn_rate 2.5-3.0 / lifetime 3.5-4.0 / bullet_speed 130-150</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>dot</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>法师系/巫医，强制玩家持续位移</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>charge_dash</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>直线冲撞</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>healer</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>sniper</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>狙击</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>蓄力高伤穿透弹</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>crystal_sentry</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>毒网</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>减速 45% 地面圈</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>spider</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>burst</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>陷阱爆发</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>自身周围 8 点环形爆发</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>mimic_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>vanish</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>暗影偷袭</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>隐身接近玩家</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>specter</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>frenzy</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>狂暴(精英通用)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3s 攻速+50% 移速+60%</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>全部精英</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>charge</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>speed_mult 3.5-4.5 / damage_mult 1.5 / windup 0.5</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>近战突进怪（冲锋兽/魔像现身突进）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>blink_strike</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>闪现突袭</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>blink</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>radius 60-90 / damage_mult 1.2-1.6 / windup 0.6-0.9</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>高机动怪（小恶魔/幽灵），落点圈=伤害区</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>self_destruct</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>自爆</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>self_destruct</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>radius 70-90 / damage_mult 2.0-2.5 / windup 0.8-1.0 / 蓄力红光闪烁</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>低血量高威胁（爆裂者），先杀后躲</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>summon_ally</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>召唤</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>summon_minions</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>summon_id（新增参数，指定召唤对象）/ count 1-2 / windup 0.7</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>无（起手演出即可）</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>精英/巫医系，制造数量压力</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>zone_ground</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>范围圈</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>root_zone</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>radius 70-90 / duration 2-3 / dps_mult 0.03-0.05 或 status=slow（新增参数）</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>区域控制（毒蛛毒网/冲锋兽践踏）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>erupt_point</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>落点喷发</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>lava_eruption</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>count 1-3 / radius 40-55 / delay 0.4-0.6 / damage_mult 1.0-1.4</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>远程压制（哥布林投石/魔像陷阱）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ring_mini</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>微型弹环</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ring_barrage</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>shots 6-8 / waves 1 / bullet_speed 150-170 / windup 0.7-0.9</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>dot</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>法师系（巫师奥术环），弹量克制不封死</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>shield_up</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>格挡护甲</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>self_buff</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>armor 0.3-0.5 / duration 2-3 / 可选 counter=true 反弹近战</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>无（金色闪光）</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>坦克型（骷髅/魔像方块），拖长击杀时间</t>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>冲锋(精英池)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>蓄力直线冲刺</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>精英池</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>治疗(精英池)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>回 3% 最大生命</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>精英池</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>summon</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>召唤(精英池)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>召唤同类弱化小怪</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>精英池</t>
         </is>
       </c>
     </row>

--- a/docs/design/怪物数据表.xlsx
+++ b/docs/design/怪物数据表.xlsx
@@ -518,6 +518,381 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -544,6 +919,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -569,6 +947,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -594,6 +975,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -619,6 +1003,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -644,6 +1031,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -669,6 +1059,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -965,7 +1358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1038,7 +1431,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
+    <row r="2" ht="40" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>slime</t>
@@ -1088,7 +1481,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>bat</t>
@@ -1136,7 +1529,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>ghost</t>
@@ -1186,7 +1579,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>goblin</t>
@@ -1236,7 +1629,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>goblin_archer</t>
@@ -1284,7 +1677,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>skeleton</t>
@@ -1334,7 +1727,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>imp</t>
@@ -1382,7 +1775,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>wizard</t>
@@ -1430,7 +1823,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>bomber</t>
@@ -1480,7 +1873,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>charger</t>
@@ -1530,7 +1923,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>healer</t>
@@ -1580,7 +1973,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
+    <row r="13" ht="40" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>crystal_sentry</t>
@@ -1628,7 +2021,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="42" customHeight="1">
+    <row r="14" ht="40" customHeight="1">
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>spider</t>
@@ -1678,7 +2071,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="42" customHeight="1">
+    <row r="15" ht="40" customHeight="1">
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>mimic_block</t>
@@ -1726,7 +2119,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="42" customHeight="1">
+    <row r="16" ht="40" customHeight="1">
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>specter</t>
@@ -1771,6 +2164,786 @@
       <c r="M16" s="2" t="inlineStr">
         <is>
           <t>level_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>rat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>巨鼠</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>32</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>118</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>gnaw_charge</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>gnaw_charge+????(??DOT)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>10</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>level_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>mushroom</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>孢菇</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>55</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>52</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>spore_fan</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>spore_fan+???(??45%)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>11</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>level_1,level_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>wolf</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>灰狼</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E19" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" t="n">
+        <v>112</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>pounce</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>pounce+????</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>12</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>level_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>treant_sapling</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>树苗守卫</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>110</v>
+      </c>
+      <c r="E20" t="n">
+        <v>13</v>
+      </c>
+      <c r="F20" t="n">
+        <v>46</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>root_zone</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>root_zone+????</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>15</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>level_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>cultist</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>邪教徒</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>65</v>
+      </c>
+      <c r="E21" t="n">
+        <v>14</v>
+      </c>
+      <c r="F21" t="n">
+        <v>62</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>triple</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>triple+???</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>13</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>level_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bone_arbalest</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>骨弩哨塔</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>75</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>fan_shot</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>fan_shot+???</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>14</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>level_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>gravedigger</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>掘墓者</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>85</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11</v>
+      </c>
+      <c r="F23" t="n">
+        <v>58</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>raise</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>raise+????</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>level_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>lava_lizard</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>熔岩蜥蜴</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>70</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16</v>
+      </c>
+      <c r="F24" t="n">
+        <v>104</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>fire_charge</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>fire_charge+????</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>13</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>level_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>fire_wisp</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>火灵</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>45</v>
+      </c>
+      <c r="E25" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" t="n">
+        <v>88</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ring_mini</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ring_mini+????</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>12</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>level_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>obsidian_golem</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>黑曜石魔像</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>130</v>
+      </c>
+      <c r="E26" t="n">
+        <v>17</v>
+      </c>
+      <c r="F26" t="n">
+        <v>42</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>self_buff</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>self_buff+??8?</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>16</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>level_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>temple_guardian</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>神殿守卫</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>105</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F27" t="n">
+        <v>60</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>shield_charge</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>shield_charge+???</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>15</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>level_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>mummy</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>木乃伊</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>95</v>
+      </c>
+      <c r="E28" t="n">
+        <v>13</v>
+      </c>
+      <c r="F28" t="n">
+        <v>56</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>curse_homing</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>curse_homing+?????</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>14</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>level_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>scarab</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>圣甲虫</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>38</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9</v>
+      </c>
+      <c r="F29" t="n">
+        <v>120</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>charge</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>charge+???</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>10</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>level_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>void_slime</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>虚空史莱姆</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>70</v>
+      </c>
+      <c r="E30" t="n">
+        <v>12</v>
+      </c>
+      <c r="F30" t="n">
+        <v>70</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>split+????</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" t="n">
+        <v>13</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>level_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>shadow_stalker</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>暗影刺客</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>55</v>
+      </c>
+      <c r="E31" t="n">
+        <v>15</v>
+      </c>
+      <c r="F31" t="n">
+        <v>100</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>stealth_ambush</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>stealth_ambush+???</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" t="n">
+        <v>14</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>level_5</t>
         </is>
       </c>
     </row>
